--- a/IPPU/A1_Outputs/A-O_Parametrization_Natural_COMPLETED.xlsx
+++ b/IPPU/A1_Outputs/A-O_Parametrization_Natural_COMPLETED.xlsx
@@ -3845,82 +3845,82 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>0.2149</v>
+        <v>0</v>
       </c>
       <c r="J37">
-        <v>0.252</v>
+        <v>0</v>
       </c>
       <c r="K37">
-        <v>0.2891</v>
+        <v>0</v>
       </c>
       <c r="L37">
-        <v>0.3318</v>
+        <v>0</v>
       </c>
       <c r="M37">
-        <v>0.3745</v>
+        <v>0</v>
       </c>
       <c r="N37">
-        <v>0.4237</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>0.4729</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>0.496</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>0.5191</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>0.8611</v>
+        <v>0</v>
       </c>
       <c r="S37">
-        <v>1.203</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>1.3251</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>1.9576</v>
+        <v>0</v>
       </c>
       <c r="V37">
-        <v>2.384</v>
+        <v>0</v>
       </c>
       <c r="W37">
-        <v>2.8103</v>
+        <v>0</v>
       </c>
       <c r="X37">
-        <v>3.2367</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>3.6631</v>
+        <v>0</v>
       </c>
       <c r="Z37">
-        <v>4.0895</v>
+        <v>0</v>
       </c>
       <c r="AA37">
-        <v>4.5159</v>
+        <v>0</v>
       </c>
       <c r="AB37">
-        <v>4.9422</v>
+        <v>0</v>
       </c>
       <c r="AC37">
-        <v>5.3686</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>5.3913</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>5.4026</v>
+        <v>0</v>
       </c>
       <c r="AG37">
-        <v>5.414</v>
+        <v>0</v>
       </c>
       <c r="AH37">
-        <v>5.4253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:34">
@@ -3949,82 +3949,82 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>0.2149</v>
+        <v>0</v>
       </c>
       <c r="J38">
-        <v>0.252</v>
+        <v>0</v>
       </c>
       <c r="K38">
-        <v>0.2891</v>
+        <v>0</v>
       </c>
       <c r="L38">
-        <v>0.3318</v>
+        <v>0</v>
       </c>
       <c r="M38">
-        <v>0.3745</v>
+        <v>0</v>
       </c>
       <c r="N38">
-        <v>0.4237</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>0.4729</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>0.496</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>0.5191</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>0.8611</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>1.203</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>1.3251</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>1.9576</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>2.384</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>2.8103</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>3.2367</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>3.6631</v>
+        <v>0</v>
       </c>
       <c r="Z38">
-        <v>4.0895</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>4.5159</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>4.9422</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>5.3686</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>5.3913</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>5.4026</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>5.414</v>
+        <v>0</v>
       </c>
       <c r="AH38">
-        <v>5.4253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:34">
@@ -4237,82 +4237,82 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>0.0034</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>0.0026</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="L47">
-        <v>0</v>
+        <v>0.0015</v>
       </c>
       <c r="M47">
-        <v>0</v>
+        <v>0.0011</v>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>0.0011</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>0.0012</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>0.0013</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>0.0015</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
       <c r="AH47">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
     </row>
     <row r="48" spans="1:34">
@@ -4341,82 +4341,82 @@
         <v>0</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>0.0034</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>0.0026</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>0.0015</v>
       </c>
       <c r="M48">
-        <v>0</v>
+        <v>0.0011</v>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>0.0011</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>0.0012</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>0.0013</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>0.0015</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
       <c r="AH48">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
     </row>
     <row r="49" spans="1:34">
@@ -4629,82 +4629,82 @@
         <v>0</v>
       </c>
       <c r="I57">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="J57">
-        <v>0</v>
+        <v>0.0038</v>
       </c>
       <c r="K57">
-        <v>0</v>
+        <v>0.0052</v>
       </c>
       <c r="L57">
-        <v>0</v>
+        <v>0.0069</v>
       </c>
       <c r="M57">
-        <v>0</v>
+        <v>0.0062</v>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>0.0044</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>0.0232</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>0.0359</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>0.0479</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>0.0737</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>0.0898</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>0.1059</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>0.122</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>0.1381</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>0.1541</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>0.1702</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>0.1863</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>0.2023</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>0.2028</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>0.2032</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>0.2036</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>0.204</v>
       </c>
       <c r="AH57">
-        <v>0</v>
+        <v>0.2045</v>
       </c>
     </row>
     <row r="58" spans="1:34">
@@ -4733,82 +4733,82 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>0</v>
+        <v>0.0043</v>
       </c>
       <c r="J58">
-        <v>0</v>
+        <v>0.0038</v>
       </c>
       <c r="K58">
-        <v>0</v>
+        <v>0.0052</v>
       </c>
       <c r="L58">
-        <v>0</v>
+        <v>0.0069</v>
       </c>
       <c r="M58">
-        <v>0</v>
+        <v>0.0062</v>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>0.0044</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>0.0232</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>0.0359</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>0.0479</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>0.0737</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>0.0898</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>0.1059</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>0.122</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>0.1381</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>0.1541</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>0.1702</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>0.1863</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>0.2023</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>0.2028</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>0.2032</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>0.2036</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>0.204</v>
       </c>
       <c r="AH58">
-        <v>0</v>
+        <v>0.2045</v>
       </c>
     </row>
     <row r="59" spans="1:34">
@@ -5021,82 +5021,82 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>0</v>
+        <v>0.0091</v>
       </c>
       <c r="J67">
-        <v>0</v>
+        <v>0.0108</v>
       </c>
       <c r="K67">
-        <v>0</v>
+        <v>0.0126</v>
       </c>
       <c r="L67">
-        <v>0</v>
+        <v>0.0137</v>
       </c>
       <c r="M67">
-        <v>0</v>
+        <v>0.0101</v>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>0.0067</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>0.0063</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>0.0954</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>0.1172</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>0.1854</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>0.2258</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>0.2662</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>0.3066</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>0.3469</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>0.3873</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>0.4277</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>0.4681</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>0.5085</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>0.5117</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>0.5128</v>
       </c>
       <c r="AH67">
-        <v>0</v>
+        <v>0.5139</v>
       </c>
     </row>
     <row r="68" spans="1:34">
@@ -5125,82 +5125,82 @@
         <v>0</v>
       </c>
       <c r="I68">
-        <v>0</v>
+        <v>0.0091</v>
       </c>
       <c r="J68">
-        <v>0</v>
+        <v>0.0108</v>
       </c>
       <c r="K68">
-        <v>0</v>
+        <v>0.0126</v>
       </c>
       <c r="L68">
-        <v>0</v>
+        <v>0.0137</v>
       </c>
       <c r="M68">
-        <v>0</v>
+        <v>0.0101</v>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>0.0067</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>0.0063</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>0.0068</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>0.0954</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>0.1172</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>0.1854</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>0.2258</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>0.2662</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>0.3066</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>0.3469</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>0.3873</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>0.4277</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>0.4681</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>0.5085</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>0.5117</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>0.5128</v>
       </c>
       <c r="AH68">
-        <v>0</v>
+        <v>0.5139</v>
       </c>
     </row>
     <row r="69" spans="1:34">
@@ -5413,82 +5413,82 @@
         <v>0</v>
       </c>
       <c r="I77">
-        <v>0</v>
+        <v>0.0794</v>
       </c>
       <c r="J77">
-        <v>0</v>
+        <v>0.0906</v>
       </c>
       <c r="K77">
-        <v>0</v>
+        <v>0.1235</v>
       </c>
       <c r="L77">
-        <v>0</v>
+        <v>0.1658</v>
       </c>
       <c r="M77">
-        <v>0</v>
+        <v>0.2255</v>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>0.2765</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>0.3072</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>0.3382</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>0.3628</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>0.3978</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>0.427</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>0.4122</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>0.4691</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>0.5713</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>0.6735</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>0.8778</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.0822</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.1844</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>1.2865</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.2893</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.292</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.2947</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>1.2974</v>
       </c>
       <c r="AH77">
-        <v>0</v>
+        <v>1.3001</v>
       </c>
     </row>
     <row r="78" spans="1:34">
@@ -5517,82 +5517,82 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>0</v>
+        <v>0.0794</v>
       </c>
       <c r="J78">
-        <v>0</v>
+        <v>0.0906</v>
       </c>
       <c r="K78">
-        <v>0</v>
+        <v>0.1235</v>
       </c>
       <c r="L78">
-        <v>0</v>
+        <v>0.1658</v>
       </c>
       <c r="M78">
-        <v>0</v>
+        <v>0.2255</v>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>0.2765</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>0.3072</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>0.3382</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>0.3628</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>0.3978</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>0.427</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>0.4122</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>0.4691</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>0.5713</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>0.6735</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>0.8778</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.0822</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>1.1844</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>1.2865</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.2893</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.292</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.2947</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>1.2974</v>
       </c>
       <c r="AH78">
-        <v>0</v>
+        <v>1.3001</v>
       </c>
     </row>
     <row r="79" spans="1:34">
@@ -5805,82 +5805,82 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>0</v>
+        <v>0.0078</v>
       </c>
       <c r="J87">
-        <v>0</v>
+        <v>0.0109</v>
       </c>
       <c r="K87">
-        <v>0</v>
+        <v>0.0125</v>
       </c>
       <c r="L87">
-        <v>0</v>
+        <v>0.0094</v>
       </c>
       <c r="M87">
-        <v>0</v>
+        <v>0.0063</v>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>0.0086</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>0.0039</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>0.0409</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>0.1464</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>0.1783</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>0.2101</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>0.242</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>0.2739</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>0.3058</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>0.3377</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>0.3696</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>0.4014</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>0.4023</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>0.4031</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>0.404</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>0.4048</v>
       </c>
       <c r="AH87">
-        <v>0</v>
+        <v>0.4057</v>
       </c>
     </row>
     <row r="88" spans="1:34">
@@ -5909,82 +5909,82 @@
         <v>0</v>
       </c>
       <c r="I88">
-        <v>0</v>
+        <v>0.0078</v>
       </c>
       <c r="J88">
-        <v>0</v>
+        <v>0.0109</v>
       </c>
       <c r="K88">
-        <v>0</v>
+        <v>0.0125</v>
       </c>
       <c r="L88">
-        <v>0</v>
+        <v>0.0094</v>
       </c>
       <c r="M88">
-        <v>0</v>
+        <v>0.0063</v>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>0.0086</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>0.0039</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>0.0409</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>0.1464</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>0.1783</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>0.2101</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>0.242</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>0.2739</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>0.3058</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>0.3377</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>0.3696</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>0.4014</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>0.4023</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>0.4031</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>0.404</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>0.4048</v>
       </c>
       <c r="AH88">
-        <v>0</v>
+        <v>0.4057</v>
       </c>
     </row>
     <row r="89" spans="1:34">
@@ -6206,73 +6206,73 @@
         <v>0</v>
       </c>
       <c r="L97">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="M97">
-        <v>0</v>
+        <v>0.0014</v>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>0.0014</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>0.0014</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>0.0014</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>0.0022</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>0.0024</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>0.0029</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>0.0033</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>0.0038</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>0.0042</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>0.0046</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>0.0056</v>
       </c>
       <c r="AH97">
-        <v>0</v>
+        <v>0.0056</v>
       </c>
     </row>
     <row r="98" spans="1:34">
@@ -6310,73 +6310,73 @@
         <v>0</v>
       </c>
       <c r="L98">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="M98">
-        <v>0</v>
+        <v>0.0014</v>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>0.0014</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>0.0014</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>0.0014</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>0.0022</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>0.0024</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>0.0029</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>0.0033</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>0.0038</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>0.0042</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>0.0046</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>0.0055</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>0.0056</v>
       </c>
       <c r="AH98">
-        <v>0</v>
+        <v>0.0056</v>
       </c>
     </row>
     <row r="99" spans="1:34">
@@ -12732,13 +12732,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF70CCF9-B41A-479B-B583-873C9821600C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F72442E5-C0D6-467E-AD08-0F0D89194E97}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20F8FCAE-EF7B-4036-BE25-642F04634515}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{226EE191-5FED-490F-B953-C9674D355E0D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6F74A62-AA34-4619-9BFD-5F9710A465FA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D68E04E2-3CE6-486E-8802-AB3C131EF82D}"/>
 </file>